--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr autoCompressPictures="1"/>
   <bookViews>
     <workbookView windowHeight="15560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" fullPrecision="0" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -27,42 +27,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="118">
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>ChineseSimplified</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>ChineseTraditional</t>
-  </si>
-  <si>
-    <t>Korean</t>
-  </si>
-  <si>
-    <t>Game.Name</t>
-  </si>
-  <si>
-    <t>星际力量</t>
-  </si>
-  <si>
-    <t>STAR FORCE</t>
-  </si>
-  <si>
-    <t>星際力量</t>
-  </si>
-  <si>
-    <t>게임 프레임워크</t>
-  </si>
-  <si>
-    <t>Game.Description</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="134">
+  <si>
+    <t xml:space="preserve">##</t>
+  </si>
+  <si>
+    <t xml:space="preserve">key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChineseSimplified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChineseTraditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game.Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">星际力量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAR FORCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">星際力量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">게임 프레임워크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game.Description</t>
   </si>
   <si>
     <r>
@@ -80,11 +80,11 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>演示程序</t>
-    </r>
-  </si>
-  <si>
-    <t>Game Framework Demo Program</t>
+      <t xml:space="preserve">演示程序</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Game Framework Demo Program</t>
   </si>
   <si>
     <r>
@@ -102,7 +102,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>演示程式</t>
+      <t xml:space="preserve">演示程式</t>
     </r>
   </si>
   <si>
@@ -121,7 +121,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>데모</t>
+      <t xml:space="preserve">데모</t>
     </r>
     <r>
       <rPr>
@@ -137,17 +137,17 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>프로그램</t>
-    </r>
-  </si>
-  <si>
-    <t>Game.Website</t>
-  </si>
-  <si>
-    <t>https://GameFramework.cn/</t>
-  </si>
-  <si>
-    <t>Game.Summary</t>
+      <t xml:space="preserve">프로그램</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Game.Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://GameFramework.cn/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game.Summary</t>
   </si>
   <si>
     <r>
@@ -157,7 +157,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>这是一个使用</t>
+      <t xml:space="preserve">这是一个使用</t>
     </r>
     <r>
       <rPr>
@@ -174,11 +174,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>游戏框架制作的游戏演示项目，目的是对此游戏框架的使用方法做一些示范，供使用者参考。</t>
-    </r>
-  </si>
-  <si>
-    <t>This project is a demo game made with Game Framework. It's intended to demonstrate how this game framework should be used for developers' reference.</t>
+      <t xml:space="preserve">游戏框架制作的游戏演示项目，目的是对此游戏框架的使用方法做一些示范，供使用者参考。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">This project is a demo game made with Game Framework. It's intended to demonstrate how this game framework should be used for developers' reference.</t>
   </si>
   <si>
     <r>
@@ -188,7 +188,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>這是一個使用</t>
+      <t xml:space="preserve">這是一個使用</t>
     </r>
     <r>
       <rPr>
@@ -205,7 +205,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>遊戲框架製作的遊戲演示專案，目的是對此遊戲框架的使用方法做一些示範，供使用者參考。</t>
+      <t xml:space="preserve">遊戲框架製作的遊戲演示專案，目的是對此遊戲框架的使用方法做一些示範，供使用者參考。</t>
     </r>
   </si>
   <si>
@@ -216,7 +216,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>이 데모는</t>
+      <t xml:space="preserve">이 데모는</t>
     </r>
     <r>
       <rPr>
@@ -233,7 +233,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>게임 시스템을 사용하여 만든 게임 데모 입니다</t>
+      <t xml:space="preserve">게임 시스템을 사용하여 만든 게임 데모 입니다</t>
     </r>
     <r>
       <rPr>
@@ -241,7 +241,7 @@
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
-      <t>.</t>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -250,7 +250,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>게임 시스템의 사용방법을 설명해 드리기 위해 예를 들어 만든 데모이기에 사용방법을 참조해 주시길 바랍니다</t>
+      <t xml:space="preserve">게임 시스템의 사용방법을 설명해 드리기 위해 예를 들어 만든 데모이기에 사용방법을 참조해 주시길 바랍니다</t>
     </r>
     <r>
       <rPr>
@@ -258,11 +258,11 @@
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Game.Introduction</t>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Game.Introduction</t>
   </si>
   <si>
     <r>
@@ -280,7 +280,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>是基于</t>
+      <t xml:space="preserve">是基于</t>
     </r>
     <r>
       <rPr>
@@ -297,11 +297,11 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>引擎的游戏框架，主要对游戏开发过程中常用模块进行了封装，很大程度地规范开发过程、加快开发速度并保证产品质量。</t>
-    </r>
-  </si>
-  <si>
-    <t>Game Framework is literally a game framework, based on Unity game engine. It encapsulates commonly used game modules during development, and, to a large degree, standardises the process, enhances the development speed and ensures the product quality.</t>
+      <t xml:space="preserve">引擎的游戏框架，主要对游戏开发过程中常用模块进行了封装，很大程度地规范开发过程、加快开发速度并保证产品质量。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Game Framework is literally a game framework, based on Unity game engine. It encapsulates commonly used game modules during development, and, to a large degree, standardises the process, enhances the development speed and ensures the product quality.</t>
   </si>
   <si>
     <r>
@@ -319,7 +319,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>是基於</t>
+      <t xml:space="preserve">是基於</t>
     </r>
     <r>
       <rPr>
@@ -336,7 +336,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>引擎的遊戲框架，主要對遊戲開發過程中常用模組進行了封裝，很大程度地規範開發過程、加快開發速度並保證產品品質。</t>
+      <t xml:space="preserve">引擎的遊戲框架，主要對遊戲開發過程中常用模組進行了封裝，很大程度地規範開發過程、加快開發速度並保證產品品質。</t>
     </r>
   </si>
   <si>
@@ -355,7 +355,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>는</t>
+      <t xml:space="preserve">는</t>
     </r>
     <r>
       <rPr>
@@ -371,7 +371,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>유니티</t>
+      <t xml:space="preserve">유니티</t>
     </r>
     <r>
       <rPr>
@@ -387,7 +387,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>엔진</t>
+      <t xml:space="preserve">엔진</t>
     </r>
     <r>
       <rPr>
@@ -404,7 +404,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>버전을</t>
+      <t xml:space="preserve">버전을</t>
     </r>
     <r>
       <rPr>
@@ -420,7 +420,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>이용한</t>
+      <t xml:space="preserve">이용한</t>
     </r>
     <r>
       <rPr>
@@ -436,7 +436,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>게임</t>
+      <t xml:space="preserve">게임</t>
     </r>
     <r>
       <rPr>
@@ -452,7 +452,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>시스템</t>
+      <t xml:space="preserve">시스템</t>
     </r>
     <r>
       <rPr>
@@ -468,7 +468,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>입니다</t>
+      <t xml:space="preserve">입니다</t>
     </r>
     <r>
       <rPr>
@@ -485,7 +485,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>주로</t>
+      <t xml:space="preserve">주로</t>
     </r>
     <r>
       <rPr>
@@ -501,7 +501,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>게임</t>
+      <t xml:space="preserve">게임</t>
     </r>
     <r>
       <rPr>
@@ -517,7 +517,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>개발과정에서</t>
+      <t xml:space="preserve">개발과정에서</t>
     </r>
     <r>
       <rPr>
@@ -533,7 +533,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>자주</t>
+      <t xml:space="preserve">자주</t>
     </r>
     <r>
       <rPr>
@@ -549,7 +549,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>사용하는</t>
+      <t xml:space="preserve">사용하는</t>
     </r>
     <r>
       <rPr>
@@ -565,7 +565,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>모듈을</t>
+      <t xml:space="preserve">모듈을</t>
     </r>
     <r>
       <rPr>
@@ -581,7 +581,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>캡슐화</t>
+      <t xml:space="preserve">캡슐화</t>
     </r>
     <r>
       <rPr>
@@ -597,7 +597,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>하여</t>
+      <t xml:space="preserve">하여</t>
     </r>
     <r>
       <rPr>
@@ -613,7 +613,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>개발</t>
+      <t xml:space="preserve">개발</t>
     </r>
     <r>
       <rPr>
@@ -629,7 +629,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>과정을</t>
+      <t xml:space="preserve">과정을</t>
     </r>
     <r>
       <rPr>
@@ -645,7 +645,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>규범화</t>
+      <t xml:space="preserve">규범화</t>
     </r>
     <r>
       <rPr>
@@ -661,7 +661,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>하고</t>
+      <t xml:space="preserve">하고</t>
     </r>
     <r>
       <rPr>
@@ -677,7 +677,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>개발</t>
+      <t xml:space="preserve">개발</t>
     </r>
     <r>
       <rPr>
@@ -693,7 +693,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>속도를</t>
+      <t xml:space="preserve">속도를</t>
     </r>
     <r>
       <rPr>
@@ -709,7 +709,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>높이며</t>
+      <t xml:space="preserve">높이며</t>
     </r>
     <r>
       <rPr>
@@ -725,7 +725,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>게임의</t>
+      <t xml:space="preserve">게임의</t>
     </r>
     <r>
       <rPr>
@@ -741,7 +741,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>콜리티를</t>
+      <t xml:space="preserve">콜리티를</t>
     </r>
     <r>
       <rPr>
@@ -757,7 +757,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>보장해</t>
+      <t xml:space="preserve">보장해</t>
     </r>
     <r>
       <rPr>
@@ -773,7 +773,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>드릴</t>
+      <t xml:space="preserve">드릴</t>
     </r>
     <r>
       <rPr>
@@ -789,7 +789,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>수</t>
+      <t xml:space="preserve">수</t>
     </r>
     <r>
       <rPr>
@@ -805,7 +805,7 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>있습니다</t>
+      <t xml:space="preserve">있습니다</t>
     </r>
     <r>
       <rPr>
@@ -814,122 +814,122 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Menu.StartButton</t>
-  </si>
-  <si>
-    <t>开始</t>
-  </si>
-  <si>
-    <t>START</t>
-  </si>
-  <si>
-    <t>開始</t>
-  </si>
-  <si>
-    <t>시작</t>
-  </si>
-  <si>
-    <t>Menu.SettingButton</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>SETTINGS</t>
-  </si>
-  <si>
-    <t>設置</t>
-  </si>
-  <si>
-    <t>설정</t>
-  </si>
-  <si>
-    <t>Menu.AboutButton</t>
-  </si>
-  <si>
-    <t>关于</t>
-  </si>
-  <si>
-    <t>ABOUT</t>
-  </si>
-  <si>
-    <t>關於</t>
-  </si>
-  <si>
-    <t>정보</t>
-  </si>
-  <si>
-    <t>Menu.QuitButton</t>
-  </si>
-  <si>
-    <t>退出</t>
-  </si>
-  <si>
-    <t>QUIT</t>
-  </si>
-  <si>
-    <t>아웃</t>
-  </si>
-  <si>
-    <t>Dialog.ConfirmButton</t>
-  </si>
-  <si>
-    <t>确定</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>確定</t>
-  </si>
-  <si>
-    <t>확인</t>
-  </si>
-  <si>
-    <t>Dialog.CancelButton</t>
-  </si>
-  <si>
-    <t>取消</t>
-  </si>
-  <si>
-    <t>CANCEL</t>
-  </si>
-  <si>
-    <t>취소</t>
-  </si>
-  <si>
-    <t>Dialog.OtherButton</t>
-  </si>
-  <si>
-    <t>ForceUpdate.Title</t>
-  </si>
-  <si>
-    <t>强制更新</t>
-  </si>
-  <si>
-    <t>OUT OF DATE</t>
-  </si>
-  <si>
-    <t>強制更新</t>
-  </si>
-  <si>
-    <t>필수 업데이트</t>
-  </si>
-  <si>
-    <t>ForceUpdate.Message</t>
-  </si>
-  <si>
-    <t>当前游戏版本过旧，是否前往更新？</t>
-  </si>
-  <si>
-    <t>The current game version is out-of-date. Would you like to go for update now?</t>
-  </si>
-  <si>
-    <t>當前遊戲版本過舊，是否前往更新？</t>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Menu.StartButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">开始</t>
+  </si>
+  <si>
+    <t xml:space="preserve">START</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開始</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menu.SettingButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">设置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SETTINGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">설정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menu.AboutButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABOUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">關於</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정보</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menu.QuitButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">退出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아웃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog.ConfirmButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">确定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">確定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog.CancelButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取消</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">취소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog.OtherButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForceUpdate.Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">强制更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT OF DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">強制更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">필수 업데이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForceUpdate.Message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当前游戏版本过旧，是否前往更新？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The current game version is out-of-date. Would you like to go for update now?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">當前遊戲版本過舊，是否前往更新？</t>
   </si>
   <si>
     <r>
@@ -939,7 +939,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>새로운 게임 버전이 있는데 업데이트를 원하십니까</t>
+      <t xml:space="preserve">새로운 게임 버전이 있는데 업데이트를 원하십니까</t>
     </r>
     <r>
       <rPr>
@@ -947,50 +947,50 @@
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <t>ForceUpdate.UpdateButton</t>
-  </si>
-  <si>
-    <t>更新</t>
-  </si>
-  <si>
-    <t>UPDATE</t>
-  </si>
-  <si>
-    <t>업데이트</t>
-  </si>
-  <si>
-    <t>ForceUpdate.QuitButton</t>
-  </si>
-  <si>
-    <t>AskQuitGame.Title</t>
-  </si>
-  <si>
-    <t>确认退出</t>
-  </si>
-  <si>
-    <t>CONFIRM TO QUIT</t>
-  </si>
-  <si>
-    <t>確認退出</t>
-  </si>
-  <si>
-    <t>아웃 확인</t>
-  </si>
-  <si>
-    <t>AskQuitGame.Message</t>
-  </si>
-  <si>
-    <t>是否确认退出游戏？</t>
-  </si>
-  <si>
-    <t>Are you sure to quit the game?</t>
-  </si>
-  <si>
-    <t>是否確認退出遊戲？</t>
+      <t xml:space="preserve">?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ForceUpdate.UpdateButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPDATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">업데이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForceUpdate.QuitButton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AskQuitGame.Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">确认退出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIRM TO QUIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">確認退出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아웃 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AskQuitGame.Message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否确认退出游戏？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are you sure to quit the game?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否確認退出遊戲？</t>
   </si>
   <si>
     <r>
@@ -1000,7 +1000,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>게임 로그아웃을 원하십니까</t>
+      <t xml:space="preserve">게임 로그아웃을 원하십니까</t>
     </r>
     <r>
       <rPr>
@@ -1008,50 +1008,50 @@
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <t>Setting.Title</t>
-  </si>
-  <si>
-    <t>Setting.Music</t>
-  </si>
-  <si>
-    <t>音乐</t>
-  </si>
-  <si>
-    <t>Music</t>
-  </si>
-  <si>
-    <t>音樂</t>
-  </si>
-  <si>
-    <t>음악</t>
-  </si>
-  <si>
-    <t>Setting.Sound</t>
-  </si>
-  <si>
-    <t>音效</t>
-  </si>
-  <si>
-    <t>Sound FX</t>
-  </si>
-  <si>
-    <t>효과음</t>
-  </si>
-  <si>
-    <t>Setting.UISound</t>
-  </si>
-  <si>
-    <t>界面音效</t>
-  </si>
-  <si>
-    <t>UI Sound FX</t>
-  </si>
-  <si>
-    <t>介面音效</t>
+      <t xml:space="preserve">?</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting.Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting.Music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">音乐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">音樂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">음악</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting.Sound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">音效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sound FX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">효과음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting.UISound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">界面音效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI Sound FX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">介面音效</t>
   </si>
   <si>
     <r>
@@ -1069,77 +1069,125 @@
         <rFont val="MS Gothic"/>
         <charset val="134"/>
       </rPr>
-      <t>효과음</t>
-    </r>
-  </si>
-  <si>
-    <t>Setting.Language</t>
-  </si>
-  <si>
-    <t>语言</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>語言</t>
-  </si>
-  <si>
-    <t>언어</t>
-  </si>
-  <si>
-    <t>Setting.LanguageTips</t>
-  </si>
-  <si>
-    <t>更改语言需要重启游戏</t>
-  </si>
-  <si>
-    <t>Language change demands restarting.</t>
-  </si>
-  <si>
-    <t>更改語言需要重啟遊戲</t>
-  </si>
-  <si>
-    <t>사용언어를 바꾼후 리부팅이 필요 합니다</t>
-  </si>
-  <si>
-    <t>/apple</t>
-  </si>
-  <si>
-    <t>苹果</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>蘋果</t>
-  </si>
-  <si>
-    <t>사과</t>
-  </si>
-  <si>
-    <t>test1</t>
-  </si>
-  <si>
-    <t>测试1</t>
-  </si>
-  <si>
-    <t>test2</t>
-  </si>
-  <si>
-    <t>测试2</t>
-  </si>
-  <si>
-    <t>1test</t>
-  </si>
-  <si>
-    <t>1测试</t>
+      <t xml:space="preserve">효과음</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting.Language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">语言</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">語言</t>
+  </si>
+  <si>
+    <t xml:space="preserve">언어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting.LanguageTips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更改语言需要重启游戏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language change demands restarting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更改語言需要重啟遊戲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용언어를 바꾼후 리부팅이 필요 합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">苹果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蘋果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测试1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测试2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1测试</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FairyDemo.Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDK 多语言标题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDK Localized Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDK 多語言標題</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDK 다국어 제목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FairyDemo.Subtitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本地化桥已接通</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localization bridge connected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本地化橋已接通</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로컬라이제이션 브리지 연결됨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FairyDemo.StatusLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">运行时状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runtime status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運行時狀態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">런타임 상태</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1161,26 +1209,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1196,7 +1244,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1227,7 +1275,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1235,7 +1283,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1243,7 +1291,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1251,14 +1299,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1266,42 +1314,42 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1622,156 +1670,156 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" xfId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1834,8 +1882,8 @@
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2097,7 +2145,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="8.83035714285714" defaultRowHeight="16.8" outlineLevelCol="5"/>
@@ -2148,7 +2196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:6">
+    <row r="3" spans="1:6" ht="17">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>11</v>
@@ -2184,7 +2232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:6">
+    <row r="5" spans="1:6" ht="17">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>18</v>
@@ -2202,7 +2250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:6">
+    <row r="6" spans="1:6" ht="17">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>23</v>
@@ -2356,7 +2404,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:6">
+    <row r="15" spans="1:6" ht="17">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -2428,7 +2476,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:6">
+    <row r="19" spans="1:6" ht="17">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>77</v>
@@ -2500,7 +2548,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="1:6">
+    <row r="23" spans="1:6" ht="17">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>92</v>
@@ -2595,9 +2643,61 @@
         <v>117</v>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" t="s">
+        <v>132</v>
+      </c>
+      <c r="F32" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>